--- a/Configs/GameConfig/Datas/gameplay_node.xlsx
+++ b/Configs/GameConfig/Datas/gameplay_node.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="57">
   <si>
     <t>##var</t>
   </si>
@@ -148,13 +148,13 @@
     <t>Root</t>
   </si>
   <si>
-    <t>10001_dia_你想吃什么</t>
+    <t>10000_dia_你想吃什么</t>
   </si>
   <si>
     <t>Dialogue</t>
   </si>
   <si>
-    <t>10001_dia_都可以</t>
+    <t>10000_dia_都可以</t>
   </si>
   <si>
     <t>张三</t>
@@ -163,7 +163,7 @@
     <t>你想吃什么</t>
   </si>
   <si>
-    <t>10001_dia_汉堡和麻辣烫选一个</t>
+    <t>10000_dia_汉堡和麻辣烫选一个</t>
   </si>
   <si>
     <t>我</t>
@@ -172,7 +172,7 @@
     <t>都可以</t>
   </si>
   <si>
-    <t>10001_choice_汉堡和麻辣烫</t>
+    <t>10000_choice_汉堡和麻辣烫</t>
   </si>
   <si>
     <t>汉堡和麻辣烫选一个</t>
@@ -181,40 +181,61 @@
     <t>Choice</t>
   </si>
   <si>
-    <t>10001_dia_汉堡太贵了|10001_dia_那就麻辣烫呗</t>
+    <t>10000_dia_汉堡太贵了|10001_dia_那就麻辣烫呗</t>
   </si>
   <si>
     <t>汉堡吧;0|麻辣烫吧;1</t>
   </si>
   <si>
-    <t>10001_dia_汉堡太贵了</t>
-  </si>
-  <si>
-    <t>10001_dia_那就麻辣烫呗</t>
+    <t>10000_dia_汉堡太贵了</t>
+  </si>
+  <si>
+    <t>10000_dia_那就麻辣烫呗</t>
   </si>
   <si>
     <t>汉堡太贵了</t>
   </si>
   <si>
-    <t>10001_dia_GOGO</t>
+    <t>10000_dia_GOGO</t>
   </si>
   <si>
     <t>那就麻辣烫呗</t>
   </si>
   <si>
+    <t>10000_end</t>
+  </si>
+  <si>
+    <t>GOGO</t>
+  </si>
+  <si>
+    <t>10000_dia_我也这么觉得</t>
+  </si>
+  <si>
+    <t>我也这么觉得，GOGO</t>
+  </si>
+  <si>
+    <t>End</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>10001_dia_第一天</t>
+  </si>
+  <si>
     <t>10001_end</t>
   </si>
   <si>
-    <t>GOGO</t>
-  </si>
-  <si>
-    <t>10001_dia_我也这么觉得</t>
-  </si>
-  <si>
-    <t>我也这么觉得，GOGO</t>
-  </si>
-  <si>
-    <t>End</t>
+    <t>第一天，无事</t>
+  </si>
+  <si>
+    <t>10002_dia_第二天</t>
+  </si>
+  <si>
+    <t>10002_end</t>
+  </si>
+  <si>
+    <t>第二天，无事</t>
   </si>
 </sst>
 </file>
@@ -1177,7 +1198,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.225" customWidth="1"/>
@@ -1308,12 +1329,11 @@
     </row>
     <row r="6" spans="2:6">
       <c r="B6" s="3">
-        <v>10001</v>
+        <v>10000</v>
       </c>
       <c r="C6" s="3">
-        <v>10001</v>
-      </c>
-      <c r="D6"/>
+        <v>10000</v>
+      </c>
       <c r="E6" t="s">
         <v>26</v>
       </c>
@@ -1326,7 +1346,7 @@
         <v>27</v>
       </c>
       <c r="C7" s="3">
-        <v>10001</v>
+        <v>10000</v>
       </c>
       <c r="E7" t="s">
         <v>28</v>
@@ -1346,9 +1366,8 @@
         <v>29</v>
       </c>
       <c r="C8" s="3">
-        <v>10001</v>
-      </c>
-      <c r="D8"/>
+        <v>10000</v>
+      </c>
       <c r="E8" t="s">
         <v>28</v>
       </c>
@@ -1367,9 +1386,8 @@
         <v>32</v>
       </c>
       <c r="C9" s="3">
-        <v>10001</v>
-      </c>
-      <c r="D9"/>
+        <v>10000</v>
+      </c>
       <c r="E9" t="s">
         <v>28</v>
       </c>
@@ -1388,9 +1406,8 @@
         <v>35</v>
       </c>
       <c r="C10" s="3">
-        <v>10001</v>
-      </c>
-      <c r="D10"/>
+        <v>10000</v>
+      </c>
       <c r="E10" t="s">
         <v>37</v>
       </c>
@@ -1406,9 +1423,8 @@
         <v>40</v>
       </c>
       <c r="C11" s="3">
-        <v>10001</v>
-      </c>
-      <c r="D11"/>
+        <v>10000</v>
+      </c>
       <c r="E11" t="s">
         <v>28</v>
       </c>
@@ -1427,9 +1443,8 @@
         <v>41</v>
       </c>
       <c r="C12" s="3">
-        <v>10001</v>
-      </c>
-      <c r="D12"/>
+        <v>10000</v>
+      </c>
       <c r="E12" t="s">
         <v>28</v>
       </c>
@@ -1448,7 +1463,7 @@
         <v>43</v>
       </c>
       <c r="C13" s="3">
-        <v>10001</v>
+        <v>10000</v>
       </c>
       <c r="E13" t="s">
         <v>28</v>
@@ -1468,7 +1483,7 @@
         <v>47</v>
       </c>
       <c r="C14" s="3">
-        <v>10001</v>
+        <v>10000</v>
       </c>
       <c r="E14" t="s">
         <v>28</v>
@@ -1488,11 +1503,108 @@
         <v>45</v>
       </c>
       <c r="C15" s="3">
-        <v>10001</v>
+        <v>10000</v>
       </c>
       <c r="E15" t="s">
         <v>49</v>
       </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17" s="3">
+        <v>10001</v>
+      </c>
+      <c r="C17" s="3">
+        <v>10001</v>
+      </c>
+      <c r="E17" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="B18" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="3">
+        <v>10001</v>
+      </c>
+      <c r="E18" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18" t="s">
+        <v>52</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" spans="2:8">
+      <c r="B19" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="3">
+        <v>10001</v>
+      </c>
+      <c r="E19" t="s">
+        <v>49</v>
+      </c>
+      <c r="H19" s="3"/>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" customFormat="1" spans="2:8">
+      <c r="B21" s="3">
+        <v>10002</v>
+      </c>
+      <c r="C21" s="3">
+        <v>10002</v>
+      </c>
+      <c r="E21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F21" t="s">
+        <v>54</v>
+      </c>
+      <c r="H21" s="3"/>
+    </row>
+    <row r="22" customFormat="1" spans="2:8">
+      <c r="B22" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="3">
+        <v>10002</v>
+      </c>
+      <c r="E22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F22" t="s">
+        <v>55</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" customFormat="1" spans="2:8">
+      <c r="B23" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="3">
+        <v>10002</v>
+      </c>
+      <c r="E23" t="s">
+        <v>49</v>
+      </c>
+      <c r="H23" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Configs/GameConfig/Datas/gameplay_node.xlsx
+++ b/Configs/GameConfig/Datas/gameplay_node.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="60">
   <si>
     <t>##var</t>
   </si>
@@ -236,6 +236,15 @@
   </si>
   <si>
     <t>第二天，无事</t>
+  </si>
+  <si>
+    <t>20001_dia_饿</t>
+  </si>
+  <si>
+    <t>20001_end</t>
+  </si>
+  <si>
+    <t>老哥，好饿，什么时候吃饭</t>
   </si>
 </sst>
 </file>
@@ -1198,7 +1207,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.225" customWidth="1"/>
@@ -1207,8 +1216,8 @@
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
     <col min="6" max="6" width="44.625" customWidth="1"/>
-    <col min="7" max="7" width="20.5" customWidth="1"/>
-    <col min="8" max="8" width="19.25" style="3" customWidth="1"/>
+    <col min="7" max="7" width="24.75" customWidth="1"/>
+    <col min="8" max="8" width="23.5" style="3" customWidth="1"/>
     <col min="9" max="9" width="35.125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1606,6 +1615,55 @@
       </c>
       <c r="H23" s="3"/>
     </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" customFormat="1" spans="2:8">
+      <c r="B25" s="3">
+        <v>20001</v>
+      </c>
+      <c r="C25" s="3">
+        <v>20001</v>
+      </c>
+      <c r="E25" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" t="s">
+        <v>57</v>
+      </c>
+      <c r="H25" s="3"/>
+    </row>
+    <row r="26" customFormat="1" spans="2:8">
+      <c r="B26" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C26" s="3">
+        <v>20001</v>
+      </c>
+      <c r="E26" t="s">
+        <v>28</v>
+      </c>
+      <c r="F26" t="s">
+        <v>58</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="27" customFormat="1" spans="2:8">
+      <c r="B27" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" s="3">
+        <v>20001</v>
+      </c>
+      <c r="E27" t="s">
+        <v>49</v>
+      </c>
+      <c r="H27" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
